--- a/sheets/조재수대금교본/검수/가시버시 사랑 대금 카덴자.xlsx
+++ b/sheets/조재수대금교본/검수/가시버시 사랑 대금 카덴자.xlsx
@@ -1211,13 +1211,13 @@
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋∼
-–∧</t>
+–</t>
         </is>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽淋湳
+          <t xml:space="preserve">淋湳
 –</t>
         </is>
       </c>
@@ -1233,7 +1233,7 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳淋∽
+          <t xml:space="preserve">湳淋
 㴌</t>
         </is>
       </c>
@@ -1315,7 +1315,7 @@
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋湳
-∧湳</t>
+湳</t>
         </is>
       </c>
       <c r="G9" s="22"/>
@@ -1331,7 +1331,7 @@
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 㳞汰</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/가시버시 사랑 대금 카덴자.xlsx
+++ b/sheets/조재수대금교본/검수/가시버시 사랑 대금 카덴자.xlsx
@@ -1211,13 +1211,13 @@
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋∼
-–</t>
+–∧</t>
         </is>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋湳
+          <t xml:space="preserve">∽淋湳
 –</t>
         </is>
       </c>
@@ -1233,7 +1233,7 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳淋
+          <t xml:space="preserve">湳淋∽
 㴌</t>
         </is>
       </c>
@@ -1315,7 +1315,7 @@
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋湳
-湳</t>
+∧湳</t>
         </is>
       </c>
       <c r="G9" s="22"/>
@@ -1331,7 +1331,7 @@
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 㳞汰</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/가시버시 사랑 대금 카덴자.xlsx
+++ b/sheets/조재수대금교본/검수/가시버시 사랑 대금 카덴자.xlsx
@@ -1175,18 +1175,18 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="46.51" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="69.11" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="G3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="69.11" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       <c r="F4" s="21"/>
       <c r="G4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="69.11" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -1250,7 +1250,7 @@
       <c r="F5" s="21"/>
       <c r="G5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="69.11" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -1259,7 +1259,7 @@
       <c r="F6" s="21"/>
       <c r="G6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="69.11" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="G7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="69.11" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="69.11" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="69.11" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       <c r="F10" s="21"/>
       <c r="G10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="69.11" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -1348,7 +1348,7 @@
       <c r="F11" s="21"/>
       <c r="G11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="69.11" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -1357,7 +1357,7 @@
       <c r="F12" s="21"/>
       <c r="G12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="69.11" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -1366,7 +1366,7 @@
       <c r="F13" s="21"/>
       <c r="G13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="69.11" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -1394,6 +1394,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="86"/>
 </worksheet>
 </file>